--- a/site-compare-skill/assets/拠点比較_テンプレート.xlsx
+++ b/site-compare-skill/assets/拠点比較_テンプレート.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>基準: {基準}</t>
+          <t>{基準}（基準があれば、ほかの拠点を基準の業務の一覧に寄せる。無ければ、拠点を横に並べて同じ業務をそろえる）</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>支持率 {支持率}</t>
+          <t>{支持率}。作り方を知らない別のエージェントが、主張を 1 つずつ原典で照合した</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>境: {境}</t>
+          <t>{境}（既定は目安。実物の拠点で数えてから直す）</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>拠点の写し: {拠点の状態}</t>
+          <t>{拠点の状態}。どれも原典照合を通した、拠点の業務フローの写し</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>作った日: {日付}</t>
+          <t>{日付}（この日のデータから書き出した）</t>
         </is>
       </c>
     </row>

--- a/site-compare-skill/assets/拠点比較_テンプレート.xlsx
+++ b/site-compare-skill/assets/拠点比較_テンプレート.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>共通＝比べた拠点のすべてに記載があり、差が無い／差異あり＝2 拠点以上に記載があり、担当・システム・帳票・判断・順序・内容のどれかが違う、または記載の無い拠点がある／拠点固有＝記載のある拠点が 1 つだけ。</t>
+          <t>共通＝比べた拠点（対象外を除く）のすべてに記載があり、差が無い／差異あり＝2 拠点以上に記載があり、担当・システム・帳票・判断・順序・内容のどれかが違う、または記載の無い拠点がある／拠点固有＝記載のある拠点が 1 つだけ。</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>○＝記載あり・差なし／△＝記載あり・差がある（基準と違う。基準が無ければ、記載のある最初の拠点と違う）／—＝資料に記載なし（業務が無いとは言っていない）／対象外＝その拠点で対象外にした業務。</t>
+          <t>○＝記載あり・差なし／△＝記載あり・差がある（基準と違う。基準が無ければ、記載のある最初の拠点と違う）／—＝資料に記載なし（業務が無いとは言っていない）／対象外＝その拠点では行わない業務・作業（資料に、ほかの拠点が行う・この拠点の手順ではないとある。業務ごと対象外にした拠点は、その業務の全部のタスク）。対象外のわけは「差の内容」の欄に出す。区分・追加の資料の依頼には数えない。</t>
         </is>
       </c>
     </row>

--- a/site-compare-skill/assets/拠点比較_テンプレート.xlsx
+++ b/site-compare-skill/assets/拠点比較_テンプレート.xlsx
@@ -45,38 +45,35 @@
   <numFmts count="0"/>
   <fonts count="7">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Yu Gothic UI"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <color rgb="00808080"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic UI"/>
       <color rgb="00C55A11"/>
       <sz val="9"/>
     </font>
